--- a/bucket_3_core_features.xlsx
+++ b/bucket_3_core_features.xlsx
@@ -3009,7 +3009,7 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -3123,7 +3123,7 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -3347,7 +3347,7 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -3415,7 +3415,7 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -3525,7 +3525,7 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>

--- a/bucket_3_core_features.xlsx
+++ b/bucket_3_core_features.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
